--- a/transport-mode/transport-mode.xlsx
+++ b/transport-mode/transport-mode.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B95C76-B223-4BEE-801B-9DE0AEEA892C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5926D73A-9D3B-4B26-A78E-54F80287A89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4155" yWindow="4155" windowWidth="21600" windowHeight="11385" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
-    <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
+    <sheet name="Vocabulary" sheetId="2" r:id="rId1"/>
+    <sheet name="Refactor Proposal" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="proposal2(PB)" sheetId="4" state="hidden" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -34,8 +37,51 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={5CEAA3FC-FAFB-4094-82AE-49C6805D3FAB}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{5CEAA3FC-FAFB-4094-82AE-49C6805D3FAB}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    I leave for discussion a list to extend the transport mode controlled vocabulary</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Petr Bureš (CZ/TTR)</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{A48F0381-E91F-484B-90FB-169229DC8605}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Petr Bureš (CZ/TTR):
+This is just to see whole picture - what do we actually need here? clearly the previous category was defined with a room for improvmement</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="392">
   <si>
     <t>ConceptScheme URI</t>
   </si>
@@ -73,19 +119,43 @@
     <t>dct:contributor</t>
   </si>
   <si>
+    <t>Petr Bures (TamTam Research)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sara Guerra de Oliveira (University of Maribor) </t>
+  </si>
+  <si>
+    <t>Ed Ooms (NDW)</t>
+  </si>
+  <si>
+    <t>Benjamin Witsch (AustriaTech)</t>
+  </si>
+  <si>
+    <t>Christian Rantzow von Huth (Vejdirektoratet)</t>
+  </si>
+  <si>
     <t>owl:versionInfo</t>
   </si>
   <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
     <t>owl:versionIRI</t>
   </si>
   <si>
+    <t>owl:priorVersion</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/transport-mode/1.0.0</t>
+  </si>
+  <si>
     <t>dct:license</t>
   </si>
   <si>
     <t>https://creativecommons.org/licenses/by/4.0/</t>
   </si>
   <si>
-    <t>My comments (not parsed by the tool).</t>
+    <t>http://purl.org/ontology/bibo/status</t>
   </si>
   <si>
     <t>URI</t>
@@ -97,104 +167,1217 @@
     <t>skos:definition</t>
   </si>
   <si>
-    <t>skos:narrower</t>
+    <t>skos:broader</t>
   </si>
   <si>
     <t>skos:notation</t>
   </si>
   <si>
+    <t>owl:deprecated^^xsd:boolean</t>
+  </si>
+  <si>
+    <t>dcterms:replacedBy</t>
+  </si>
+  <si>
+    <t>Road transport</t>
+  </si>
+  <si>
+    <t>Movement of people or goods using vehicles operating on public roads.</t>
+  </si>
+  <si>
+    <t>Car</t>
+  </si>
+  <si>
+    <t>Motor vehicle designed primarily for personal passenger transport</t>
+  </si>
+  <si>
+    <t>Motorcycle</t>
+  </si>
+  <si>
+    <t>Two‑wheeled motor vehicle for individual transport</t>
+  </si>
+  <si>
+    <t>Bus</t>
+  </si>
+  <si>
+    <t>Road vehicle designed for carrying multiple passengers on fixed or flexible routes</t>
+  </si>
+  <si>
+    <t>Express bus</t>
+  </si>
+  <si>
+    <t>Local bus</t>
+  </si>
+  <si>
+    <t>Coach</t>
+  </si>
+  <si>
+    <t>Comfortable long‑distance bus designed for intercity or touring travel</t>
+  </si>
+  <si>
+    <t>Trolleybus</t>
+  </si>
+  <si>
+    <t>Truck</t>
+  </si>
+  <si>
+    <t>Motor vehicle designed for transporting goods or heavy loads</t>
+  </si>
+  <si>
+    <t>Rail transport</t>
+  </si>
+  <si>
+    <t>Transport using guided vehicles running on rail tracks</t>
+  </si>
+  <si>
+    <t>High‑speed rail</t>
+  </si>
+  <si>
+    <t>Intercity rail</t>
+  </si>
+  <si>
+    <t>Long-distance rail</t>
+  </si>
+  <si>
+    <t>Rail service covering extended national or international routes</t>
+  </si>
+  <si>
+    <t>Regional and local rail</t>
+  </si>
+  <si>
+    <t>Rail service covering regional or local routes</t>
+  </si>
+  <si>
+    <t>Regional rail</t>
+  </si>
+  <si>
+    <t>Rail service connecting towns and smaller cities within a region.</t>
+  </si>
+  <si>
+    <t>Suburban rail</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/transport-mode/tram-light-rail</t>
+  </si>
+  <si>
+    <t>Tram and light rail</t>
+  </si>
+  <si>
+    <t>Street‑level rail vehicle operating in mixed traffic or dedicated lanes</t>
+  </si>
+  <si>
+    <t>Metro, Subway train</t>
+  </si>
+  <si>
+    <t>Metro</t>
+  </si>
+  <si>
+    <t>High‑capacity urban rail system operating on segregated tracks</t>
+  </si>
+  <si>
+    <t>Water transport</t>
+  </si>
+  <si>
+    <t>Transport using vessels on seas, rivers, or canals</t>
+  </si>
+  <si>
+    <t>Maritime</t>
+  </si>
+  <si>
+    <t>Maritime including ferry / Transport on seas or coastal waters</t>
+  </si>
+  <si>
+    <t>Inland waterways</t>
+  </si>
+  <si>
+    <t>Transport on rivers, canals, and lakes</t>
+  </si>
+  <si>
+    <t>Shuttle ferry</t>
+  </si>
+  <si>
+    <t>Vessel carrying passengers or vehicles across water on scheduled routes</t>
+  </si>
+  <si>
+    <t>Water taxi</t>
+  </si>
+  <si>
+    <t>A water taxi is a small passenger vessel that provides transportation services between points on waterways</t>
+  </si>
+  <si>
+    <t>River bus</t>
+  </si>
+  <si>
+    <t>Air transport</t>
+  </si>
+  <si>
+    <t>Movement of people or goods using aircrafts operating in the airspace</t>
+  </si>
+  <si>
     <t>Air</t>
   </si>
   <si>
+    <t>Aeroplane</t>
+  </si>
+  <si>
+    <t>Aircraft for commercial transport of people or goods over medium and long distances</t>
+  </si>
+  <si>
+    <t>Sailplane</t>
+  </si>
+  <si>
+    <t>Air taxi</t>
+  </si>
+  <si>
+    <t>A small passenger aircraft that provides on-demand or scheduled point-to-point air transportation services.</t>
+  </si>
+  <si>
+    <t>Helicopter</t>
+  </si>
+  <si>
+    <t>Gyroplane</t>
+  </si>
+  <si>
+    <t>Airship</t>
+  </si>
+  <si>
+    <t>Powered parachutes</t>
+  </si>
+  <si>
+    <t>Unmanned aircraft</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/transport-mode/special-transport</t>
+  </si>
+  <si>
+    <t>Special transport</t>
+  </si>
+  <si>
+    <t>Transport using cable‑driven or mechanically guided systems</t>
+  </si>
+  <si>
+    <t>Cableways</t>
+  </si>
+  <si>
+    <t>Funicular railways, cable cars, gondolas, chairlifts, and drag lifts</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/transport-mode/elevator</t>
+  </si>
+  <si>
+    <t>Elevator</t>
+  </si>
+  <si>
+    <t>Vertical transport device that moves passengers or goods in an enclosed cabin.</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/transport-mode/escalator</t>
+  </si>
+  <si>
+    <t>Escalator</t>
+  </si>
+  <si>
+    <t>A continuously moving inclined staircase for transporting passengers.</t>
+  </si>
+  <si>
+    <t>Seasonal transport</t>
+  </si>
+  <si>
+    <t>Seasonal or terrain‑specific transport (e.g., on snow or ice)</t>
+  </si>
+  <si>
+    <t>Micromobility</t>
+  </si>
+  <si>
+    <t>Lightweight, usually low‑speed vehicles for short‑distance travel</t>
+  </si>
+  <si>
+    <t>https://w3id.org/mobilitydcat-ap/transport-mode/bicycle</t>
+  </si>
+  <si>
+    <t>Bicycle and E-Bike</t>
+  </si>
+  <si>
+    <t>Human‑powered or electric‑assisted two‑wheel vehicle</t>
+  </si>
+  <si>
+    <t>E-Scooter</t>
+  </si>
+  <si>
+    <t>Electrically powered standing scooter</t>
+  </si>
+  <si>
+    <t>Moped</t>
+  </si>
+  <si>
+    <t>A lightweight, low-powered motorbike</t>
+  </si>
+  <si>
+    <t>Pedestrian</t>
+  </si>
+  <si>
+    <t>Movement by walking or using mobility aids</t>
+  </si>
+  <si>
+    <t>Other</t>
+  </si>
+  <si>
+    <t>Bike Hire</t>
+  </si>
+  <si>
+    <t>Bike Sharing</t>
+  </si>
+  <si>
+    <t>Car Hire</t>
+  </si>
+  <si>
+    <t>Car Pooling</t>
+  </si>
+  <si>
+    <t>Car Sharing</t>
+  </si>
+  <si>
+    <t>Ride Pooling</t>
+  </si>
+  <si>
+    <t>Taxi</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Green = Added values</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <r>
+      <t>…/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>transport-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>mode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>/air</t>
+    </r>
+  </si>
+  <si>
+    <t>not fitting here // or we would need air/rail/sea/water/land modes and I am not seeing them there</t>
+  </si>
+  <si>
+    <t>…/transport-mode/bus</t>
+  </si>
+  <si>
+    <t>…/transport-mode/coach</t>
+  </si>
+  <si>
+    <t>long distance bus</t>
+  </si>
+  <si>
+    <t>…/transport-mode/rail</t>
+  </si>
+  <si>
+    <t>Rail</t>
+  </si>
+  <si>
+    <t>…/transport-mode/long-distance-rail</t>
+  </si>
+  <si>
+    <t>…/transport-mode/high-speed-rail</t>
+  </si>
+  <si>
+    <t>…/transport-mode/intercity-rail</t>
+  </si>
+  <si>
+    <t>…/transport-mode/regional-rail</t>
+  </si>
+  <si>
+    <t>…/transport-mode/suburban-rail</t>
+  </si>
+  <si>
+    <t>…/transport-mode/tram</t>
+  </si>
+  <si>
+    <t>Tram</t>
+  </si>
+  <si>
+    <t>…/transport-mode/metro</t>
+  </si>
+  <si>
+    <t>…/transport-mode/maritime</t>
+  </si>
+  <si>
+    <t>…/transport-mode/ferry</t>
+  </si>
+  <si>
+    <t>Ferry</t>
+  </si>
+  <si>
+    <t>…/transport-mode/inland-waterway</t>
+  </si>
+  <si>
+    <t>Inland waterway</t>
+  </si>
+  <si>
+    <t>…/transport-mode/cableway</t>
+  </si>
+  <si>
+    <t>Cableway</t>
+  </si>
+  <si>
+    <t>…/transport-mode/funicular</t>
+  </si>
+  <si>
+    <t>Funicular</t>
+  </si>
+  <si>
+    <t>…/transport-mode/trolleybus</t>
+  </si>
+  <si>
+    <t>…/transport-mode/bicycle</t>
+  </si>
+  <si>
     <t>Bicycle</t>
   </si>
   <si>
-    <t>Bike Hire</t>
-  </si>
-  <si>
-    <t>Bike Sharing</t>
-  </si>
-  <si>
-    <t>Bus</t>
-  </si>
-  <si>
-    <t>Car</t>
-  </si>
-  <si>
-    <t>Car Hire</t>
-  </si>
-  <si>
-    <t>Car Pooling</t>
-  </si>
-  <si>
-    <t>Car Sharing</t>
-  </si>
-  <si>
-    <t>E-Scooter</t>
-  </si>
-  <si>
-    <t>Long-distance coach</t>
-  </si>
-  <si>
-    <t>Long-distance rail</t>
-  </si>
-  <si>
-    <t>Metro, Subway train</t>
-  </si>
-  <si>
-    <t>Motorcycle</t>
-  </si>
-  <si>
-    <t>Pedestrian</t>
-  </si>
-  <si>
-    <t>Regional and local rail</t>
-  </si>
-  <si>
-    <t>Ride Pooling</t>
-  </si>
-  <si>
-    <t>Shuttle bus</t>
-  </si>
-  <si>
-    <t>Shuttle ferry</t>
-  </si>
-  <si>
-    <t>Taxi</t>
-  </si>
-  <si>
-    <t>Tram, Light rail</t>
-  </si>
-  <si>
-    <t>Truck</t>
-  </si>
-  <si>
-    <t>Other</t>
-  </si>
-  <si>
-    <t>Maritime</t>
-  </si>
-  <si>
-    <t>Maritime including ferry</t>
-  </si>
-  <si>
-    <t>http://purl.org/ontology/bibo/status</t>
-  </si>
-  <si>
-    <t>owl:priorVersion</t>
-  </si>
-  <si>
-    <t>Published Controlled Vocabulary</t>
-  </si>
-  <si>
-    <t>1.0.0</t>
+    <t>…/transport-mode/motorcycle</t>
+  </si>
+  <si>
+    <t>…/transport-mode/car</t>
+  </si>
+  <si>
+    <t>…/transport-mode/pedestrian</t>
+  </si>
+  <si>
+    <t>…/transport-mode/scooter</t>
+  </si>
+  <si>
+    <t>Scooter</t>
+  </si>
+  <si>
+    <t>…/transport-mode/e-scooter</t>
+  </si>
+  <si>
+    <t>E‑Scooter</t>
+  </si>
+  <si>
+    <t>…/transport-mode/lift</t>
+  </si>
+  <si>
+    <t>Lift</t>
+  </si>
+  <si>
+    <t>like in a bulding?</t>
+  </si>
+  <si>
+    <t>…/transport-mode/snow-ice</t>
+  </si>
+  <si>
+    <t>Snow &amp; Ice</t>
+  </si>
+  <si>
+    <t>meaning?</t>
+  </si>
+  <si>
+    <t>…/transport-mode/truck</t>
+  </si>
+  <si>
+    <t>…/transport-mode/local-bus</t>
+  </si>
+  <si>
+    <t>…/transport-mode/express-bus</t>
+  </si>
+  <si>
+    <t>…/transport-mode/river-bus</t>
+  </si>
+  <si>
+    <t>river boat?</t>
+  </si>
+  <si>
+    <t>…/transport-mode/gondola</t>
+  </si>
+  <si>
+    <t>Gondola</t>
+  </si>
+  <si>
+    <t>…/transport-mode/chairlift</t>
+  </si>
+  <si>
+    <t>Chairlift</t>
+  </si>
+  <si>
+    <t>…/transport-mode/drag-lift</t>
+  </si>
+  <si>
+    <t>Drag lift</t>
+  </si>
+  <si>
+    <t>…/transport-mode/other</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>…/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>access-model</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/car-sharing</t>
+    </r>
+  </si>
+  <si>
+    <t>…/access-model/car-pooling</t>
+  </si>
+  <si>
+    <t>…/access-model/car-hire</t>
+  </si>
+  <si>
+    <t>…/access-model/bike-sharing</t>
+  </si>
+  <si>
+    <t>…/access-model/bike-hire</t>
+  </si>
+  <si>
+    <t>…/access-model/ride-pooling</t>
+  </si>
+  <si>
+    <t>…/access-model/scooter-sharing</t>
+  </si>
+  <si>
+    <t>Scooter Sharing</t>
+  </si>
+  <si>
+    <t>…/access-model/e-scooter-sharing</t>
+  </si>
+  <si>
+    <t>E‑Scooter Sharing</t>
+  </si>
+  <si>
+    <t>…/access-model/free-floating</t>
+  </si>
+  <si>
+    <t>Free‑floating</t>
+  </si>
+  <si>
+    <t>…/access-model/station-based</t>
+  </si>
+  <si>
+    <t>Station‑based</t>
+  </si>
+  <si>
+    <t>…/access-model/peer-to-peer</t>
+  </si>
+  <si>
+    <t>Peer‑to‑peer</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>…/</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>service-type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>/scheduled</t>
+    </r>
+  </si>
+  <si>
+    <t>Scheduled</t>
+  </si>
+  <si>
+    <t>public</t>
+  </si>
+  <si>
+    <t>…/service-type/semi-scheduled</t>
+  </si>
+  <si>
+    <t>Semi‑scheduled</t>
+  </si>
+  <si>
+    <t>…/service-type/unscheduled</t>
+  </si>
+  <si>
+    <t>Unscheduled</t>
+  </si>
+  <si>
+    <t>…/service-type/on-demand</t>
+  </si>
+  <si>
+    <t>On‑demand</t>
+  </si>
+  <si>
+    <t>DATEX: public transport:This service is running only on demand</t>
+  </si>
+  <si>
+    <t>…/service-type/flexible</t>
+  </si>
+  <si>
+    <t>Flexible</t>
+  </si>
+  <si>
+    <t>…/service-type/fixed-route</t>
+  </si>
+  <si>
+    <t>Fixed route</t>
+  </si>
+  <si>
+    <t>…/service-type/door-to-door</t>
+  </si>
+  <si>
+    <t>Door‑to‑door</t>
+  </si>
+  <si>
+    <t>…/service-type/taxi</t>
+  </si>
+  <si>
+    <t>…/service-type/drt</t>
+  </si>
+  <si>
+    <t>Demand responsive transport (DRT) / Dial‑a‑Ride</t>
+  </si>
+  <si>
+    <t>…/service-type/shuttle</t>
+  </si>
+  <si>
+    <t>Shuttle Service</t>
+  </si>
+  <si>
+    <t>DATEX:Shuttle services are in place, usually to reach a specific destination or event.</t>
+  </si>
+  <si>
+    <t>Transport Modes</t>
+  </si>
+  <si>
+    <t>Transport using guided vehicles running on rail tracks.</t>
+  </si>
+  <si>
+    <t>Movement of people or goods using aircrafts operating in the airspace.</t>
+  </si>
+  <si>
+    <t>Transport using vessels on seas, rivers, or canals.</t>
+  </si>
+  <si>
+    <t>Cable &amp; special transport</t>
+  </si>
+  <si>
+    <t>Transport using cable‑driven or mechanically guided systems.</t>
+  </si>
+  <si>
+    <t>Lightweight, usually low‑speed vehicles for short‑distance travel.</t>
+  </si>
+  <si>
+    <t>Movement by walking or using mobility aids.</t>
+  </si>
+  <si>
+    <t>Other and seasonal transport mode</t>
+  </si>
+  <si>
+    <t>Category for modes not covered elsewhere.</t>
+  </si>
+  <si>
+    <t>Motor vehicle designed primarily for personal passenger transport.</t>
+  </si>
+  <si>
+    <t>Personal motor vehicle</t>
+  </si>
+  <si>
+    <t>PrivateVehicle</t>
+  </si>
+  <si>
+    <t>VehicleType: car</t>
+  </si>
+  <si>
+    <t>Two‑wheeled motor vehicle for individual transport.</t>
+  </si>
+  <si>
+    <t>Two‑wheel motor vehicle</t>
+  </si>
+  <si>
+    <t>VehicleType: motorcycle</t>
+  </si>
+  <si>
+    <t>Road vehicle designed for carrying multiple passengers on fixed or flexible routes.</t>
+  </si>
+  <si>
+    <t>Passenger road vehicle</t>
+  </si>
+  <si>
+    <t>VehicleType: bus</t>
+  </si>
+  <si>
+    <t>Comfortable long‑distance bus designed for intercity or touring travel.</t>
+  </si>
+  <si>
+    <t>Long‑distance bus</t>
+  </si>
+  <si>
+    <t>VehicleType: coach</t>
+  </si>
+  <si>
+    <t>Electric bus drawing power from overhead wires.</t>
+  </si>
+  <si>
+    <t>Electric bus on wires</t>
+  </si>
+  <si>
+    <t>TrolleyBus</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Motor vehicle designed for transporting goods or heavy loads.</t>
+  </si>
+  <si>
+    <t>Goods vehicle</t>
+  </si>
+  <si>
+    <t>GoodsVehicle</t>
+  </si>
+  <si>
+    <t>VehicleType: heavyGoodsVehicle</t>
+  </si>
+  <si>
+    <t>Bus operating frequent, short‑distance urban services with many stops.</t>
+  </si>
+  <si>
+    <t>Urban bus with frequent stops</t>
+  </si>
+  <si>
+    <t>Bus operating longer routes with limited stops for faster travel.</t>
+  </si>
+  <si>
+    <t>Limited‑stop bus</t>
+  </si>
+  <si>
+    <t>Rail service operating at very high speeds on dedicated lines.</t>
+  </si>
+  <si>
+    <t>&gt;250 km/h</t>
+  </si>
+  <si>
+    <t>RailSubmode: highSpeedRail</t>
+  </si>
+  <si>
+    <t>Rail service connecting major cities over medium to long distances.</t>
+  </si>
+  <si>
+    <t>City‑to‑city</t>
+  </si>
+  <si>
+    <t>RailSubmode: intercityRail</t>
+  </si>
+  <si>
+    <t>Long‑distance rail</t>
+  </si>
+  <si>
+    <t>Rail service covering extended national or international routes.</t>
+  </si>
+  <si>
+    <t>Extended routes</t>
+  </si>
+  <si>
+    <t>RailSubmode: longDistanceRail</t>
+  </si>
+  <si>
+    <t>Regional services</t>
+  </si>
+  <si>
+    <t>RailSubmode: regionalRail</t>
+  </si>
+  <si>
+    <t>Frequent rail service connecting suburbs with urban centers.</t>
+  </si>
+  <si>
+    <t>Commuter rail</t>
+  </si>
+  <si>
+    <t>RailSubmode: suburbanRail</t>
+  </si>
+  <si>
+    <t>Street‑level rail vehicle operating in mixed traffic or dedicated lanes.</t>
+  </si>
+  <si>
+    <t>Street rail</t>
+  </si>
+  <si>
+    <t>PublicTransportMode: tram</t>
+  </si>
+  <si>
+    <t>High‑capacity urban rail system operating on segregated tracks.</t>
+  </si>
+  <si>
+    <t>Urban rapid transit</t>
+  </si>
+  <si>
+    <t>PublicTransportMode: metro</t>
+  </si>
+  <si>
+    <t>Balloons</t>
+  </si>
+  <si>
+    <t>Maritime transport</t>
+  </si>
+  <si>
+    <t>Transport on seas or coastal waters.</t>
+  </si>
+  <si>
+    <t>Sea/coastal</t>
+  </si>
+  <si>
+    <t>WaterSubmode: waterTransport</t>
+  </si>
+  <si>
+    <t>VehicleType: vessel</t>
+  </si>
+  <si>
+    <t>Transport on rivers, canals, and lakes.</t>
+  </si>
+  <si>
+    <t>Rivers/canals</t>
+  </si>
+  <si>
+    <t>WaterSubmode: inlandWaterways</t>
+  </si>
+  <si>
+    <t>VehicleType: inlandWaterwayVessel</t>
+  </si>
+  <si>
+    <t>Vessel carrying passengers or vehicles across water on scheduled routes.</t>
+  </si>
+  <si>
+    <t>Passenger/vehicle ferry</t>
+  </si>
+  <si>
+    <t>WaterSubmode: ferry</t>
+  </si>
+  <si>
+    <t>VehicleType: ferry</t>
+  </si>
+  <si>
+    <t>Passenger vessel providing urban or suburban water‑based transit.</t>
+  </si>
+  <si>
+    <t>Urban water transit</t>
+  </si>
+  <si>
+    <t>WaterSubmode: waterBus</t>
+  </si>
+  <si>
+    <t>Aerial cable transport system for passengers or goods.</t>
+  </si>
+  <si>
+    <t>Cable‑driven system</t>
+  </si>
+  <si>
+    <r>
+      <t>Telecabin</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <charset val="238"/>
+      </rPr>
+      <t>CableCar</t>
+    </r>
+  </si>
+  <si>
+    <t>Enclosed cabin suspended from a moving cable.</t>
+  </si>
+  <si>
+    <t>Enclosed cabin</t>
+  </si>
+  <si>
+    <t>Telecabin</t>
+  </si>
+  <si>
+    <t>Open or semi‑open seat suspended from a cable, mainly for slopes.</t>
+  </si>
+  <si>
+    <t>Open chair</t>
+  </si>
+  <si>
+    <t>ChairLift</t>
+  </si>
+  <si>
+    <t>Rail vehicle pulled by cable on steep inclines.</t>
+  </si>
+  <si>
+    <t>Cable rail on incline</t>
+  </si>
+  <si>
+    <t>Surface lift pulling skiers uphill.</t>
+  </si>
+  <si>
+    <t>Ski surface lift</t>
+  </si>
+  <si>
+    <t>DragLift</t>
+  </si>
+  <si>
+    <t>Lift (elevator)</t>
+  </si>
+  <si>
+    <t>Vertical transport system inside buildings or structures.</t>
+  </si>
+  <si>
+    <t>Vertical lift</t>
+  </si>
+  <si>
+    <t>Human‑powered or electric‑assisted two‑wheel vehicle.</t>
+  </si>
+  <si>
+    <t>Human‑powered or e‑assist</t>
+  </si>
+  <si>
+    <t>Cycle</t>
+  </si>
+  <si>
+    <t>VehicleType: bicycle</t>
+  </si>
+  <si>
+    <t>Small platform vehicle propelled by foot or motor.</t>
+  </si>
+  <si>
+    <t>Small platform vehicle</t>
+  </si>
+  <si>
+    <t>MicroMobilityDevice</t>
+  </si>
+  <si>
+    <t>Electrically powered standing scooter.</t>
+  </si>
+  <si>
+    <t>Electric scooter</t>
+  </si>
+  <si>
+    <t>Snow &amp; ice transport</t>
+  </si>
+  <si>
+    <t>Seasonal or terrain‑specific transport on snow or ice.</t>
+  </si>
+  <si>
+    <t>Snow/ice vehicles</t>
+  </si>
+  <si>
+    <t>SnowMobile</t>
+  </si>
+  <si>
+    <t>VehicleType: snowplough / winterMaintenanceVehicle</t>
+  </si>
+  <si>
+    <t>other</t>
+  </si>
+  <si>
+    <t>Unclassified</t>
+  </si>
+  <si>
+    <t>OtherMode</t>
+  </si>
+  <si>
+    <t>VehicleType: other</t>
+  </si>
+  <si>
+    <t>Shared Mobility Service</t>
+  </si>
+  <si>
+    <t>Mobility provided through shared access to vehicles instead of ownership.</t>
+  </si>
+  <si>
+    <t>Car sharing</t>
+  </si>
+  <si>
+    <t>Short‑term access to shared cars, usually via app.</t>
+  </si>
+  <si>
+    <t>Shared cars</t>
+  </si>
+  <si>
+    <t>VehicleSharingService</t>
+  </si>
+  <si>
+    <t>Car pooling</t>
+  </si>
+  <si>
+    <t>Multiple passengers sharing a private car for a trip.</t>
+  </si>
+  <si>
+    <t>Shared private car</t>
+  </si>
+  <si>
+    <t>RideSharingService</t>
+  </si>
+  <si>
+    <t>Car hire</t>
+  </si>
+  <si>
+    <t>Rental of a car for hours or days.</t>
+  </si>
+  <si>
+    <t>Rental</t>
+  </si>
+  <si>
+    <t>VehicleRentalService</t>
+  </si>
+  <si>
+    <t>Bike sharing</t>
+  </si>
+  <si>
+    <t>Shared bicycles available for short‑term use.</t>
+  </si>
+  <si>
+    <t>Shared bikes</t>
+  </si>
+  <si>
+    <t>CycleSharingService</t>
+  </si>
+  <si>
+    <t>Bike hire</t>
+  </si>
+  <si>
+    <t>Rental of bicycles for longer periods.</t>
+  </si>
+  <si>
+    <t>CycleRentalService</t>
+  </si>
+  <si>
+    <t>Scooter sharing</t>
+  </si>
+  <si>
+    <t>Shared scooters available for short trips.</t>
+  </si>
+  <si>
+    <t>Shared scooters</t>
+  </si>
+  <si>
+    <t>MicroMobilitySharingService</t>
+  </si>
+  <si>
+    <t>E‑scooter sharing</t>
+  </si>
+  <si>
+    <t>Shared electric scooters available via app.</t>
+  </si>
+  <si>
+    <t>Shared e‑scooters</t>
+  </si>
+  <si>
+    <t>Service model</t>
+  </si>
+  <si>
+    <t>Operational model describing how shared vehicles are accessed.</t>
+  </si>
+  <si>
+    <t>Vehicles can be picked up and dropped off anywhere within a zone.</t>
+  </si>
+  <si>
+    <t>Vehicles must be picked up and returned to designated stations.</t>
+  </si>
+  <si>
+    <t>Private owners rent out their vehicles to others.</t>
+  </si>
+  <si>
+    <t>Transport service type</t>
+  </si>
+  <si>
+    <t>How a transport service is organized, scheduled, and delivered.</t>
+  </si>
+  <si>
+    <t>Services operating according to a fixed timetable.</t>
+  </si>
+  <si>
+    <t>Fixed timetable</t>
+  </si>
+  <si>
+    <t>ScheduledService</t>
+  </si>
+  <si>
+    <t>PublicTransportSchedule</t>
+  </si>
+  <si>
+    <t>Services with partial timetable constraints or flexible timing.</t>
+  </si>
+  <si>
+    <t>Partial timetable</t>
+  </si>
+  <si>
+    <t>FlexibleService</t>
+  </si>
+  <si>
+    <t>Services without a fixed timetable.</t>
+  </si>
+  <si>
+    <t>No timetable</t>
+  </si>
+  <si>
+    <t>UnscheduledService</t>
+  </si>
+  <si>
+    <t>Services following a predefined route.</t>
+  </si>
+  <si>
+    <t>Predefined route</t>
+  </si>
+  <si>
+    <t>FixedRoute</t>
+  </si>
+  <si>
+    <t>Route</t>
+  </si>
+  <si>
+    <t>Services with variable routing depending on demand.</t>
+  </si>
+  <si>
+    <t>Variable routing</t>
+  </si>
+  <si>
+    <t>FlexibleRoute</t>
+  </si>
+  <si>
+    <t>Services activated only when requested by users.</t>
+  </si>
+  <si>
+    <t>Triggered by request</t>
+  </si>
+  <si>
+    <t>DemandResponsiveService</t>
+  </si>
+  <si>
+    <t>DemandResponsiveTransport</t>
+  </si>
+  <si>
+    <t>Services picking up and dropping off passengers at specific locations.</t>
+  </si>
+  <si>
+    <t>Point‑to‑point</t>
+  </si>
+  <si>
+    <t>DoorToDoorService</t>
+  </si>
+  <si>
+    <t>Licensed vehicle providing point‑to‑point transport on demand.</t>
+  </si>
+  <si>
+    <t>Licensed on‑demand</t>
+  </si>
+  <si>
+    <t>TaxiService</t>
+  </si>
+  <si>
+    <t>VehicleType: taxi</t>
+  </si>
+  <si>
+    <t>Demand responsive transport (DRT)</t>
+  </si>
+  <si>
+    <t>Shared, flexible service responding to user requests.</t>
+  </si>
+  <si>
+    <t>Shared flexible service</t>
+  </si>
+  <si>
+    <t>Shuttle service</t>
+  </si>
+  <si>
+    <t>Repeated transport between fixed points, often for events or airports.</t>
+  </si>
+  <si>
+    <t>Repeated fixed‑point service</t>
+  </si>
+  <si>
+    <t>ShuttleService</t>
+  </si>
+  <si>
+    <t>Draft Controlled Vocabulary</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,8 +1407,73 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -235,6 +1483,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -252,7 +1536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -269,6 +1553,67 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -285,6 +1630,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Sara Filipa Guerra De Oliveira" id="{BFE87DCA-1858-4F22-9352-7A96F9858869}" userId="S::sara.guerraoliveira_um.si#ext#@rupprechtconsultde.onmicrosoft.com::9e0df386-993b-4e86-95d7-9935cc62ab2c" providerId="AD"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -572,26 +1923,26 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2026-02-18T20:19:23.80" personId="{BFE87DCA-1858-4F22-9352-7A96F9858869}" id="{5CEAA3FC-FAFB-4094-82AE-49C6805D3FAB}">
+    <text>I leave for discussion a list to extend the transport mode controlled vocabulary</text>
+  </threadedComment>
+</ThreadedComments>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:G58"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="89.42578125" customWidth="1"/>
-    <col min="2" max="2" width="74.7109375" customWidth="1"/>
-    <col min="3" max="3" width="26.7109375" customWidth="1"/>
-    <col min="4" max="4" width="45.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="65" customWidth="1"/>
+    <col min="2" max="2" width="60.28515625" customWidth="1"/>
+    <col min="3" max="3" width="85.28515625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="71.85546875" style="1" customWidth="1"/>
     <col min="5" max="5" width="35.85546875" style="1" customWidth="1"/>
     <col min="6" max="6" width="30.42578125" customWidth="1"/>
+    <col min="7" max="7" width="55.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -609,7 +1960,7 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
@@ -618,7 +1969,7 @@
       <c r="B3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="27"/>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -627,7 +1978,7 @@
       <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="27"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -636,7 +1987,7 @@
       <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="27"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -645,353 +1996,2521 @@
       <c r="B6" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="27"/>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="27"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="27"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="C9" s="27"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" t="str">
-        <f>_xlfn.CONCAT(B1,"/",B9)</f>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/1.0.0</v>
-      </c>
-      <c r="C10" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="27"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="1"/>
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="27"/>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="1"/>
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="27"/>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="str">
+        <f>_xlfn.CONCAT(B1,"/",B12)</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/2.0.0</v>
+      </c>
+      <c r="C13" s="27"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="27"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="27"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="str">
+        <f t="shared" ref="A20:A58" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B20)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="2"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="str">
+        <f t="shared" ref="A21:A28" si="1">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B21)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" t="str">
+        <f>A20</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="str">
+        <f t="shared" si="1"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/motorcycle</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" t="str">
+        <f>A20</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="str">
+        <f t="shared" si="1"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/bus</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" t="str">
+        <f>A20</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="str">
+        <f t="shared" si="1"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/coach</v>
+      </c>
+      <c r="B24" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" s="14" t="str">
+        <f>A20</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
+      </c>
+      <c r="E24" s="15"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="str">
+        <f t="shared" si="1"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/truck</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" t="str">
+        <f>A20</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="str">
+        <f t="shared" si="1"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
+      </c>
+      <c r="B26" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="str">
-        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B19)," ","-"),",",""))</f>
+      <c r="C26" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="str">
+        <f t="shared" si="1"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/long-distance-rail</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C27" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="D27" s="1" t="str">
+        <f>A26</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="33" t="str">
+        <f t="shared" si="1"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/regional-and-local-rail</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="1" t="str">
+        <f>A26</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
+      </c>
+      <c r="E28" s="32"/>
+    </row>
+    <row r="29" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="32" t="str">
+        <f>A26</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
+      </c>
+      <c r="E29" s="32"/>
+    </row>
+    <row r="30" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="str">
+        <f t="shared" ref="A30:A36" si="2">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B30)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/metro-subway-train</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" s="9" t="str">
+        <f>A31</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/metro</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/metro</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="15" t="str">
+        <f>A26</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
+      </c>
+      <c r="E31" s="15"/>
+    </row>
+    <row r="32" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
+      </c>
+      <c r="B32" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/maritime</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="1" t="str">
+        <f>A32</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/inland-waterways</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="1" t="str">
+        <f>A32</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/shuttle-ferry</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="1" t="str">
+        <f>A32</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="str">
+        <f t="shared" si="2"/>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-taxi</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D36" s="15" t="str">
+        <f>A32</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
+      </c>
+      <c r="E36" s="15"/>
+    </row>
+    <row r="37" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="str">
+        <f t="shared" ref="A37" si="3">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B37)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
+      </c>
+      <c r="B37" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+    </row>
+    <row r="38" spans="1:7" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="str">
+        <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="str">
-        <f t="shared" ref="A20:A42" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B20)," ","-"),",",""))</f>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/bicycle</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" t="str">
+      <c r="B38" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" s="9" t="str">
+        <f>A37</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B39)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/aeroplane</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="1" t="str">
+        <f>A37</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="str">
+        <f t="shared" ref="A40" si="4">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B40)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-taxi</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="1" t="str">
+        <f>A37</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>88</v>
+      </c>
+      <c r="B41" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="C41" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B42)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/cableways</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D42" t="str">
+        <f>A41</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/special-transport</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D43" s="1" t="str">
+        <f>A41</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/special-transport</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D44" s="1" t="str">
+        <f>A41</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/special-transport</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B45)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/seasonal-transport</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D45" s="15" t="str">
+        <f>A41</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/special-transport</v>
+      </c>
+      <c r="E45" s="15"/>
+    </row>
+    <row r="46" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="28" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B46)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/micromobility</v>
+      </c>
+      <c r="B46" s="29" t="s">
+        <v>101</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+    </row>
+    <row r="47" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>103</v>
+      </c>
+      <c r="B47" s="37" t="s">
+        <v>104</v>
+      </c>
+      <c r="C47" s="37" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>A46</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/micromobility</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B48)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/e-scooter</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D48" s="15" t="str">
+        <f>A46</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/micromobility</v>
+      </c>
+      <c r="E48" s="15"/>
+    </row>
+    <row r="49" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B49)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/moped</v>
+      </c>
+      <c r="B49" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D49" s="15" t="str">
+        <f>A46</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/micromobility</v>
+      </c>
+      <c r="E49" s="15"/>
+    </row>
+    <row r="50" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="31" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B50)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/pedestrian</v>
+      </c>
+      <c r="B50" s="29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="str">
+        <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B51)," ","-"),",",""))</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/other</v>
+      </c>
+      <c r="B51" s="29" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bike-hire</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" t="str">
+      <c r="B52" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="C52" s="10"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G52" s="9" t="str">
+        <f>A47</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/bicycle</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bike-sharing</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/bus</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="str">
+      <c r="B53" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="C53" s="10"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G53" s="9" t="str">
+        <f>A47</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/bicycle</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car-hire</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" t="str">
+      <c r="B54" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="10"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G54" s="9" t="str">
+        <f>A21</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car-pooling</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="str">
+      <c r="B55" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C55" s="10"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" s="9" t="str">
+        <f>A21</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car-sharing</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/e-scooter</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/long-distance-coach</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/long-distance-rail</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/maritime</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/metro-subway-train</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/motorcycle</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/pedestrian</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/regional-and-local-rail</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" t="str">
+      <c r="B56" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C56" s="10"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" s="9" t="str">
+        <f>A21</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/ride-pooling</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/shuttle-bus</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/shuttle-ferry</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" t="str">
+      <c r="B57" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C57" s="10"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" s="9" t="str">
+        <f>A21</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/taxi</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/tram-light-rail</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/truck</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" t="str">
-        <f t="shared" si="0"/>
-        <v>https://w3id.org/mobilitydcat-ap/transport-mode/other</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>44</v>
+      <c r="B58" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C58" s="10"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="16"/>
+      <c r="F58" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" s="9" t="str">
+        <f>A21</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B1" r:id="rId1" xr:uid="{8D37ED2A-6F4C-4B2C-B212-84B5255111B4}"/>
-    <hyperlink ref="B12" r:id="rId2" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
+    <hyperlink ref="B15" r:id="rId2" xr:uid="{F5CCEF78-A2AE-420B-8B79-2E74A78B421A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:D61"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>150</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>152</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B23" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>155</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="C25" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C26" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>163</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="B28" s="13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="B29" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="B30" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="B31" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" s="6"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" s="6"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="19"/>
+      <c r="B37" s="20"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="13" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="B48" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="8"/>
+      <c r="B49" s="13"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="8"/>
+      <c r="B50" s="13"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="19"/>
+      <c r="B51" s="20"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D55" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D61" t="s">
+        <v>212</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CDCB3D0-B550-4EFC-8834-EEEBF03CEB3D}">
+  <dimension ref="A1:E92"/>
+  <sheetFormatPr defaultColWidth="55.28515625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="72.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="22"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="22"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>238</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>259</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>263</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="21"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="21"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C35" s="21"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="21"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="26" t="s">
+        <v>269</v>
+      </c>
+      <c r="C37" s="21"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="C38" s="21"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="21"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C40" s="21"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="22" t="s">
+        <v>64</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="C42" s="21"/>
+      <c r="D42" s="21"/>
+      <c r="E42" s="21"/>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>275</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>281</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="23"/>
+      <c r="E47" s="21"/>
+    </row>
+    <row r="48" spans="1:5" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="C48" s="22"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>288</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>289</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>294</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="D53" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="21"/>
+      <c r="B55" s="21"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="23"/>
+      <c r="E55" s="21"/>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C56" s="21"/>
+      <c r="D56" s="21"/>
+      <c r="E56" s="21"/>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="D58" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="E58" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="D59" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="E59" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="21"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="23"/>
+      <c r="E60" s="21"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="C61" s="22"/>
+      <c r="D61" s="21"/>
+      <c r="E61" s="21"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D62" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="E62" s="23" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>318</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="11"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="23"/>
+      <c r="E64" s="23"/>
+    </row>
+    <row r="65" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A65" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="C65" s="22"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>326</v>
+      </c>
+      <c r="E66" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="D67" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="E67" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>332</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="E69" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="E70" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="D71" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="E71" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="D72" s="23" t="s">
+        <v>345</v>
+      </c>
+      <c r="E72" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="21"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="23"/>
+      <c r="E73" s="21"/>
+    </row>
+    <row r="74" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A74" s="24" t="s">
+        <v>349</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="C74" s="21"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="21"/>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="C75" s="21"/>
+      <c r="D75" s="23"/>
+      <c r="E75" s="21"/>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C76" s="21"/>
+      <c r="D76" s="23"/>
+      <c r="E76" s="21"/>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C77" s="21"/>
+      <c r="D77" s="23"/>
+      <c r="E77" s="21"/>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="21"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="23"/>
+      <c r="E78" s="21"/>
+    </row>
+    <row r="79" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A79" s="24" t="s">
+        <v>354</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="C79" s="22"/>
+      <c r="D79" s="21"/>
+      <c r="E79" s="21"/>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>356</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="D80" s="23" t="s">
+        <v>358</v>
+      </c>
+      <c r="E80" s="23" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>360</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="D81" s="23" t="s">
+        <v>362</v>
+      </c>
+      <c r="E81" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="D82" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="E82" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="D83" s="23" t="s">
+        <v>368</v>
+      </c>
+      <c r="E83" s="23" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>370</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D84" s="23" t="s">
+        <v>372</v>
+      </c>
+      <c r="E84" s="23" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="D85" s="23" t="s">
+        <v>375</v>
+      </c>
+      <c r="E85" s="23" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="D86" s="23" t="s">
+        <v>379</v>
+      </c>
+      <c r="E86" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>380</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="D87" s="23" t="s">
+        <v>382</v>
+      </c>
+      <c r="E87" s="23" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="D88" s="23" t="s">
+        <v>376</v>
+      </c>
+      <c r="E88" s="23" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="D89" s="23" t="s">
+        <v>390</v>
+      </c>
+      <c r="E89" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="21"/>
+      <c r="B90" s="21"/>
+      <c r="C90" s="21"/>
+      <c r="D90" s="21"/>
+      <c r="E90" s="21"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="21"/>
+      <c r="B91" s="21"/>
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="21"/>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="21"/>
+      <c r="B92" s="21"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="21"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100156B981FAAFB4349A28B03AB4EEECF9F" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1e7c9bb6974a57a0073a8d48fc3b6089">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4ea66b1c-fa60-4493-a86c-b420df37761a" xmlns:ns3="322c47a9-7cf9-4f39-ba36-4bf679c08fb0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d5753863158ce54f5fdf0d8971fe3971" ns2:_="" ns3:_="">
-    <xsd:import namespace="4ea66b1c-fa60-4493-a86c-b420df37761a"/>
-    <xsd:import namespace="322c47a9-7cf9-4f39-ba36-4bf679c08fb0"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006748505E66128D48AAED90CD5CD3616F" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fc5d2d94b5e314f8d7afecc6215f6be4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa" xmlns:ns3="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f994fb40b965d01e7e08c4f92ceb61cd" ns2:_="" ns3:_="">
+    <xsd:import namespace="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+    <xsd:import namespace="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:note" minOccurs="0"/>
-                <xsd:element ref="ns3:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:Date_x002f_Heure" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -999,36 +4518,68 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="4ea66b1c-fa60-4493-a86c-b420df37761a" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="84381483-150a-4726-b180-307f5f59d12b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
       <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{517dfd69-ad1a-4b80-a735-177bb10dea14}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="4ea66b1c-fa60-4493-a86c-b420df37761a">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="18" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="14" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{4c7b0293-1299-401f-a92e-ea8ec6326420}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="13e36eaf-61a1-47aa-b343-0f7d626aa9a0">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -1038,93 +4589,6 @@
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="322c47a9-7cf9-4f39-ba36-4bf679c08fb0" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="17" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="18" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="note" ma:index="20" nillable="true" ma:displayName="note" ma:format="Dropdown" ma:internalName="note">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="84381483-150a-4726-b180-307f5f59d12b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="24" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="Date_x002f_Heure" ma:index="25" nillable="true" ma:displayName="Date/Heure" ma:format="DateTime" ma:internalName="Date_x002f_Heure">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:DateTime"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="26" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1226,19 +4690,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="4ea66b1c-fa60-4493-a86c-b420df37761a" xsi:nil="true"/>
-    <Date_x002f_Heure xmlns="322c47a9-7cf9-4f39-ba36-4bf679c08fb0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="322c47a9-7cf9-4f39-ba36-4bf679c08fb0">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <note xmlns="322c47a9-7cf9-4f39-ba36-4bf679c08fb0" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -1249,31 +4700,31 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9CAEA66D-CB51-4402-8859-C4D741E726C2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E07F1C-30C1-44FD-9041-9A393B69CD1A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
+    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{10799EA1-9D9B-4761-AC56-2401CB930EF2}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="4ea66b1c-fa60-4493-a86c-b420df37761a"/>
-    <ds:schemaRef ds:uri="322c47a9-7cf9-4f39-ba36-4bf679c08fb0"/>
+    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E07F1C-30C1-44FD-9041-9A393B69CD1A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4ea66b1c-fa60-4493-a86c-b420df37761a"/>
-    <ds:schemaRef ds:uri="322c47a9-7cf9-4f39-ba36-4bf679c08fb0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/transport-mode/transport-mode.xlsx
+++ b/transport-mode/transport-mode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scrocca\Desktop\cefriel-github\controlled-vocabularies\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5926D73A-9D3B-4B26-A78E-54F80287A89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3B11E8-9877-4033-A576-1A0FFA05F08E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="393">
   <si>
     <t>ConceptScheme URI</t>
   </si>
@@ -1371,6 +1371,9 @@
   </si>
   <si>
     <t>Draft Controlled Vocabulary</t>
+  </si>
+  <si>
+    <t>skos:narrower</t>
   </si>
 </sst>
 </file>
@@ -1536,7 +1539,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1588,9 +1591,6 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1599,9 +1599,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1613,6 +1610,27 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1933,16 +1951,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G58"/>
+  <dimension ref="A1:H58"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="65" customWidth="1"/>
     <col min="2" max="2" width="60.28515625" customWidth="1"/>
     <col min="3" max="3" width="85.28515625" style="6" customWidth="1"/>
-    <col min="4" max="4" width="71.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="35.85546875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="30.42578125" customWidth="1"/>
-    <col min="7" max="7" width="55.28515625" customWidth="1"/>
+    <col min="4" max="5" width="71.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="35.85546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" customWidth="1"/>
+    <col min="8" max="8" width="55.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -2088,324 +2106,352 @@
         <v>391</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="38" t="s">
         <v>26</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="2" t="s">
+      <c r="H19" s="2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A20" s="28" t="str">
         <f t="shared" ref="A20:A58" si="0">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B20)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
       </c>
-      <c r="B20" s="29" t="s">
+      <c r="B20" s="39" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="38" t="s">
+      <c r="C20" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D20" s="37" t="str">
+        <f>_xlfn.TEXTJOIN(",",,A21:A25)</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/car,https://w3id.org/mobilitydcat-ap/transport-mode/motorcycle,https://w3id.org/mobilitydcat-ap/transport-mode/bus,https://w3id.org/mobilitydcat-ap/transport-mode/coach,https://w3id.org/mobilitydcat-ap/transport-mode/truck</v>
+      </c>
+      <c r="E20" s="3"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="2"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="str">
         <f t="shared" ref="A21:A28" si="1">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B21)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="37" t="s">
+      <c r="C21" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="D21" t="str">
+      <c r="D21"/>
+      <c r="E21" t="str">
         <f>A20</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/motorcycle</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C22" s="37" t="s">
+      <c r="C22" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="D22" t="str">
+      <c r="D22"/>
+      <c r="E22" t="str">
         <f>A20</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bus</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="D23" t="str">
+      <c r="D23"/>
+      <c r="E23" t="str">
         <f>A20</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
       </c>
     </row>
-    <row r="24" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/coach</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="34" t="s">
         <v>42</v>
       </c>
       <c r="C24" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D24" s="14" t="str">
+      <c r="E24" s="14" t="str">
         <f>A20</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
       </c>
-      <c r="E24" s="15"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F24" s="15"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/truck</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C25" s="37" t="s">
+      <c r="C25" s="35" t="s">
         <v>46</v>
       </c>
-      <c r="D25" t="str">
+      <c r="D25"/>
+      <c r="E25" t="str">
         <f>A20</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/road-transport</v>
       </c>
     </row>
-    <row r="26" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" s="14" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A26" s="28" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
       </c>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="39" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="D26" s="15"/>
+      <c r="D26" s="15" t="str">
+        <f>_xlfn.TEXTJOIN(",",,A27:A29,A31)</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/long-distance-rail,https://w3id.org/mobilitydcat-ap/transport-mode/regional-and-local-rail,https://w3id.org/mobilitydcat-ap/transport-mode/tram-light-rail,https://w3id.org/mobilitydcat-ap/transport-mode/metro</v>
+      </c>
       <c r="E26" s="15"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F26" s="15"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/long-distance-rail</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="37" t="s">
+      <c r="C27" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="D27" s="1" t="str">
+      <c r="E27" s="1" t="str">
         <f>A26</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
       </c>
     </row>
-    <row r="28" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="33" t="str">
+    <row r="28" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="32" t="str">
         <f t="shared" si="1"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/regional-and-local-rail</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="D28" s="1" t="str">
+      <c r="D28" s="1"/>
+      <c r="E28" s="1" t="str">
         <f>A26</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
       </c>
-      <c r="E28" s="32"/>
-    </row>
-    <row r="29" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F28" s="31"/>
+    </row>
+    <row r="29" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>58</v>
       </c>
-      <c r="B29" s="37" t="s">
+      <c r="B29" s="42" t="s">
         <v>59</v>
       </c>
-      <c r="C29" s="37" t="s">
+      <c r="C29" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="D29" s="32" t="str">
+      <c r="D29" s="31"/>
+      <c r="E29" s="31" t="str">
         <f>A26</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
       </c>
-      <c r="E29" s="32"/>
-    </row>
-    <row r="30" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F29" s="31"/>
+    </row>
+    <row r="30" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="str">
         <f t="shared" ref="A30:A36" si="2">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B30)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/metro-subway-train</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="43" t="s">
         <v>61</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16"/>
-      <c r="F30" s="9" t="b">
+      <c r="F30" s="16"/>
+      <c r="G30" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G30" s="9" t="str">
+      <c r="H30" s="9" t="str">
         <f>A31</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/metro</v>
       </c>
     </row>
-    <row r="31" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/metro</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="34" t="s">
         <v>62</v>
       </c>
       <c r="C31" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="D31" s="15" t="str">
+      <c r="D31" s="15"/>
+      <c r="E31" s="15" t="str">
         <f>A26</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/rail-transport</v>
       </c>
-      <c r="E31" s="15"/>
-    </row>
-    <row r="32" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F31" s="15"/>
+    </row>
+    <row r="32" spans="1:8" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.25">
       <c r="A32" s="28" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
       </c>
-      <c r="B32" s="29" t="s">
+      <c r="B32" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="30" t="s">
+      <c r="C32" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D32" s="15"/>
+      <c r="D32" s="15" t="str">
+        <f>_xlfn.TEXTJOIN(",",,A33:A36)</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/maritime,https://w3id.org/mobilitydcat-ap/transport-mode/inland-waterways,https://w3id.org/mobilitydcat-ap/transport-mode/shuttle-ferry,https://w3id.org/mobilitydcat-ap/transport-mode/water-taxi</v>
+      </c>
       <c r="E32" s="15"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F32" s="15"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/maritime</v>
       </c>
-      <c r="B33" s="34" t="s">
+      <c r="B33" s="41" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="37" t="s">
+      <c r="C33" s="35" t="s">
         <v>67</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="E33" s="1" t="str">
         <f>A32</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/inland-waterways</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="34" t="s">
         <v>68</v>
       </c>
       <c r="C34" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="E34" s="1" t="str">
         <f>A32</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/shuttle-ferry</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="37" t="s">
+      <c r="C35" s="35" t="s">
         <v>71</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="E35" s="1" t="str">
         <f>A32</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
       </c>
     </row>
-    <row r="36" spans="1:7" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="str">
         <f t="shared" si="2"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-taxi</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="34" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="35" t="s">
+      <c r="C36" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="D36" s="15" t="str">
+      <c r="D36" s="15"/>
+      <c r="E36" s="15" t="str">
         <f>A32</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/water-transport</v>
       </c>
-      <c r="E36" s="15"/>
-    </row>
-    <row r="37" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F36" s="15"/>
+    </row>
+    <row r="37" spans="1:8" s="14" customFormat="1" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="28" t="str">
         <f t="shared" ref="A37" si="3">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B37)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
       </c>
-      <c r="B37" s="29" t="s">
+      <c r="B37" s="39" t="s">
         <v>75</v>
       </c>
       <c r="C37" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="15"/>
+      <c r="D37" s="15" t="str">
+        <f>_xlfn.TEXTJOIN(",",,A39:A40)</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/aeroplane,https://w3id.org/mobilitydcat-ap/transport-mode/air-taxi</v>
+      </c>
       <c r="E37" s="15"/>
-    </row>
-    <row r="38" spans="1:7" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F37" s="15"/>
+    </row>
+    <row r="38" spans="1:8" s="9" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="43" t="s">
         <v>77</v>
       </c>
       <c r="C38" s="10" t="s">
@@ -2413,337 +2459,358 @@
       </c>
       <c r="D38" s="16"/>
       <c r="E38" s="16"/>
-      <c r="F38" s="9" t="b">
+      <c r="F38" s="16"/>
+      <c r="G38" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G38" s="9" t="str">
+      <c r="H38" s="9" t="str">
         <f>A37</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="14" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B39)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/aeroplane</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="34" t="s">
         <v>78</v>
       </c>
       <c r="C39" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D39" s="1" t="str">
+      <c r="E39" s="1" t="str">
         <f>A37</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="str">
         <f t="shared" ref="A40" si="4">_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B40)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-taxi</v>
       </c>
-      <c r="B40" s="36" t="s">
+      <c r="B40" s="34" t="s">
         <v>81</v>
       </c>
-      <c r="C40" s="35" t="s">
+      <c r="C40" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="D40" s="1" t="str">
+      <c r="E40" s="1" t="str">
         <f>A37</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/air-transport</v>
       </c>
     </row>
-    <row r="41" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+    <row r="41" spans="1:8" s="14" customFormat="1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A41" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="B41" s="29" t="s">
+      <c r="B41" s="39" t="s">
         <v>89</v>
       </c>
       <c r="C41" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="15"/>
+      <c r="D41" s="15" t="str">
+        <f>_xlfn.TEXTJOIN(",",,A42:A45)</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/cableways,https://w3id.org/mobilitydcat-ap/transport-mode/elevator,https://w3id.org/mobilitydcat-ap/transport-mode/escalator,https://w3id.org/mobilitydcat-ap/transport-mode/seasonal-transport</v>
+      </c>
       <c r="E41" s="15"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F41" s="15"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B42)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/cableways</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="34" t="s">
         <v>91</v>
       </c>
       <c r="C42" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="D42" t="str">
+      <c r="D42"/>
+      <c r="E42" t="str">
         <f>A41</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/special-transport</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="B43" s="13" t="s">
+      <c r="B43" s="34" t="s">
         <v>94</v>
       </c>
       <c r="C43" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="D43" s="1" t="str">
+      <c r="E43" s="1" t="str">
         <f>A41</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/special-transport</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B44" s="13" t="s">
+      <c r="B44" s="34" t="s">
         <v>97</v>
       </c>
       <c r="C44" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="D44" s="1" t="str">
+      <c r="E44" s="1" t="str">
         <f>A41</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/special-transport</v>
       </c>
     </row>
-    <row r="45" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="14" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B45)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/seasonal-transport</v>
       </c>
-      <c r="B45" s="13" t="s">
+      <c r="B45" s="34" t="s">
         <v>99</v>
       </c>
       <c r="C45" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="D45" s="15" t="str">
+      <c r="D45" s="15"/>
+      <c r="E45" s="15" t="str">
         <f>A41</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/special-transport</v>
       </c>
-      <c r="E45" s="15"/>
-    </row>
-    <row r="46" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F45" s="15"/>
+    </row>
+    <row r="46" spans="1:8" s="14" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A46" s="28" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B46)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/micromobility</v>
       </c>
-      <c r="B46" s="29" t="s">
+      <c r="B46" s="39" t="s">
         <v>101</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="D46" s="15"/>
+      <c r="D46" s="15" t="str">
+        <f>_xlfn.TEXTJOIN(",",,A47:A49)</f>
+        <v>https://w3id.org/mobilitydcat-ap/transport-mode/bicycle,https://w3id.org/mobilitydcat-ap/transport-mode/e-scooter,https://w3id.org/mobilitydcat-ap/transport-mode/moped</v>
+      </c>
       <c r="E46" s="15"/>
-    </row>
-    <row r="47" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F46" s="15"/>
+    </row>
+    <row r="47" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="37" t="s">
+      <c r="B47" s="42" t="s">
         <v>104</v>
       </c>
-      <c r="C47" s="37" t="s">
+      <c r="C47" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="D47" s="1" t="str">
+      <c r="E47" s="1" t="str">
         <f>A46</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/micromobility</v>
       </c>
     </row>
-    <row r="48" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B48)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/e-scooter</v>
       </c>
-      <c r="B48" s="13" t="s">
+      <c r="B48" s="34" t="s">
         <v>106</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="D48" s="15" t="str">
+      <c r="D48" s="15"/>
+      <c r="E48" s="15" t="str">
         <f>A46</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/micromobility</v>
       </c>
-      <c r="E48" s="15"/>
-    </row>
-    <row r="49" spans="1:7" s="14" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="F48" s="15"/>
+    </row>
+    <row r="49" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B49)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/moped</v>
       </c>
-      <c r="B49" s="13" t="s">
+      <c r="B49" s="34" t="s">
         <v>108</v>
       </c>
       <c r="C49" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D49" s="15" t="str">
+      <c r="D49" s="15"/>
+      <c r="E49" s="15" t="str">
         <f>A46</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/micromobility</v>
       </c>
-      <c r="E49" s="15"/>
-    </row>
-    <row r="50" spans="1:7" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="31" t="str">
+      <c r="F49" s="15"/>
+    </row>
+    <row r="50" spans="1:8" s="32" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="30" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B50)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/pedestrian</v>
       </c>
-      <c r="B50" s="29" t="s">
+      <c r="B50" s="39" t="s">
         <v>110</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D50" s="32"/>
-      <c r="E50" s="32"/>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D50" s="31"/>
+      <c r="E50" s="31"/>
+      <c r="F50" s="31"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="str">
         <f>_xlfn.CONCAT($B$1,"/",SUBSTITUTE(SUBSTITUTE(LOWER(B51)," ","-"),",",""))</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/other</v>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="39" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bike-hire</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="43" t="s">
         <v>113</v>
       </c>
       <c r="C52" s="10"/>
       <c r="D52" s="16"/>
       <c r="E52" s="16"/>
-      <c r="F52" s="9" t="b">
+      <c r="F52" s="16"/>
+      <c r="G52" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G52" s="9" t="str">
+      <c r="H52" s="9" t="str">
         <f>A47</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bicycle</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bike-sharing</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="43" t="s">
         <v>114</v>
       </c>
       <c r="C53" s="10"/>
       <c r="D53" s="16"/>
       <c r="E53" s="16"/>
-      <c r="F53" s="9" t="b">
+      <c r="F53" s="16"/>
+      <c r="G53" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G53" s="9" t="str">
+      <c r="H53" s="9" t="str">
         <f>A47</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/bicycle</v>
       </c>
     </row>
-    <row r="54" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car-hire</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="43" t="s">
         <v>115</v>
       </c>
       <c r="C54" s="10"/>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
-      <c r="F54" s="9" t="b">
+      <c r="F54" s="16"/>
+      <c r="G54" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G54" s="9" t="str">
+      <c r="H54" s="9" t="str">
         <f>A21</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
       </c>
     </row>
-    <row r="55" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car-pooling</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="43" t="s">
         <v>116</v>
       </c>
       <c r="C55" s="10"/>
       <c r="D55" s="16"/>
       <c r="E55" s="16"/>
-      <c r="F55" s="9" t="b">
+      <c r="F55" s="16"/>
+      <c r="G55" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G55" s="9" t="str">
+      <c r="H55" s="9" t="str">
         <f>A21</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
       </c>
     </row>
-    <row r="56" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car-sharing</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="43" t="s">
         <v>117</v>
       </c>
       <c r="C56" s="10"/>
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
-      <c r="F56" s="9" t="b">
+      <c r="F56" s="16"/>
+      <c r="G56" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G56" s="9" t="str">
+      <c r="H56" s="9" t="str">
         <f>A21</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
       </c>
     </row>
-    <row r="57" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/ride-pooling</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="43" t="s">
         <v>118</v>
       </c>
       <c r="C57" s="10"/>
       <c r="D57" s="16"/>
       <c r="E57" s="16"/>
-      <c r="F57" s="9" t="b">
+      <c r="F57" s="16"/>
+      <c r="G57" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G57" s="9" t="str">
+      <c r="H57" s="9" t="str">
         <f>A21</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
       </c>
     </row>
-    <row r="58" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="str">
         <f t="shared" si="0"/>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/taxi</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="43" t="s">
         <v>119</v>
       </c>
       <c r="C58" s="10"/>
       <c r="D58" s="16"/>
       <c r="E58" s="16"/>
-      <c r="F58" s="9" t="b">
+      <c r="F58" s="16"/>
+      <c r="G58" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="G58" s="9" t="str">
+      <c r="H58" s="9" t="str">
         <f>A21</f>
         <v>https://w3id.org/mobilitydcat-ap/transport-mode/car</v>
       </c>
@@ -4479,14 +4546,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4691,21 +4756,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="13e36eaf-61a1-47aa-b343-0f7d626aa9a0" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E07F1C-30C1-44FD-9041-9A393B69CD1A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
-    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -4730,9 +4794,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{354E852E-38F4-443F-ABCC-E4BE2043727A}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00E07F1C-30C1-44FD-9041-9A393B69CD1A}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="13e36eaf-61a1-47aa-b343-0f7d626aa9a0"/>
+    <ds:schemaRef ds:uri="c386cf2f-2f8b-4d8e-84b2-f14abf7317aa"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>